--- a/r4-core-151-gda-triple/StructureDefinition-at-core-location.xlsx
+++ b/r4-core-151-gda-triple/StructureDefinition-at-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-18T14:14:36+00:00</t>
+    <t>2026-10-19T12:51:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-core-151-gda-triple/StructureDefinition-at-core-location.xlsx
+++ b/r4-core-151-gda-triple/StructureDefinition-at-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T12:51:52+00:00</t>
+    <t>2026-10-19T13:41:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -3345,10 +3345,10 @@
       </c>
       <c r="Q17" s="2"/>
       <c r="R17" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S17" t="s" s="2">
         <v>194</v>
-      </c>
-      <c r="S17" t="s" s="2">
-        <v>21</v>
       </c>
       <c r="T17" t="s" s="2">
         <v>195</v>
@@ -4313,10 +4313,10 @@
       </c>
       <c r="Q26" s="2"/>
       <c r="R26" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S26" t="s" s="2">
         <v>252</v>
-      </c>
-      <c r="S26" t="s" s="2">
-        <v>21</v>
       </c>
       <c r="T26" t="s" s="2">
         <v>21</v>
